--- a/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:06:47+00:00</t>
+    <t>2026-09-21T07:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:30:27+00:00</t>
+    <t>2026-09-21T07:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:49:30+00:00</t>
+    <t>2026-09-21T07:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:54:52+00:00</t>
+    <t>2026-09-21T08:04:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVContactPointAvailability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T08:04:47+00:00</t>
+    <t>2026-10-14T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
